--- a/output/pdf_financials_xlsx/NPV.xlsx
+++ b/output/pdf_financials_xlsx/NPV.xlsx
@@ -7189,7 +7189,11 @@
           <t>Additions to intangible assets 9 $</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -8444,7 +8448,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NPV.xlsx
+++ b/output/pdf_financials_xlsx/NPV.xlsx
@@ -928,10 +928,10 @@
         <v>-1.842734</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-6.497058</v>
+        <v>-4.284818</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-4.80777</v>
+        <v>-1.129576</v>
       </c>
     </row>
     <row r="21">
@@ -952,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-2.21224</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-3.678194</v>
       </c>
     </row>
     <row r="22">
@@ -9584,7 +9584,11 @@
           <t>Loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -9623,7 +9627,11 @@
           <t>Loss from discontinued operations 19 $</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -10337,7 +10345,11 @@
           <t>Interest revenue $</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -11555,7 +11567,11 @@
           <t>Interest revenue $ 7,346 $</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
